--- a/jobs.xlsx
+++ b/jobs.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-09-02 11:35:26</t>
+          <t>2026-09-02 12:06:56</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">

--- a/jobs.xlsx
+++ b/jobs.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-09-02 12:06:56</t>
+          <t>2026-09-02 13:05:26</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">

--- a/jobs.xlsx
+++ b/jobs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:O1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -492,69 +492,6 @@
           <t>Notes</t>
         </is>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>ea727cfe696841aa3edf</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Oracle</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>https://careers.oracle.com/en/sites/jobsearch/jobs?keyword=Software%20Engineer&amp;location=United%20States&amp;locationId=300000000149325</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>generic</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>2026-09-02 11:35:26</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2026-09-02 13:05:26</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>9a55c6d446a7838dea8c</t>
-        </is>
-      </c>
-      <c r="K2" t="n">
-        <v>35</v>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>role:Software Engineer</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/jobs.xlsx
+++ b/jobs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O1"/>
+  <dimension ref="A1:O153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -493,6 +493,8982 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>eed6ca4a2adac90795a2</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Top jobs</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>https://jobs.sap.com/topjobs/</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>1605480092531e419708</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>3f1f3fdb4bfd172d9b88</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>View all jobs</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>https://jobs.sap.com/viewalljobs/</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>e8b073dfb85af54f41fe</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>8a4f81aab4679173b1fb</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Taulia careers</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>https://taulia.com/company/careers/</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>8b0fbbee39afc0437cfe</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>eb4afc5ebffc86852d90</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Developer</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>https://developers.sap.com/</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>12d6245ea7a4328aaedd</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>bfc1c94087deec535acc</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Careers</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>https://jobs.sap.com/</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>5f5174cbed50d59d066b</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>0956548cf8cb653509b8</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Careers</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>https://www.google.com/about/careers/applications/</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>5f5174cbed50d59d066b</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>78417a8f8e4bacb4bfd2</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>work_outline work_outline Jobs Jobs</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>https://www.google.com/about/careers/applications/jobs/jobs/results</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>d8864db1c383b5703db1</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>81f6bd5bed38f45ac41c</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>person_outline person_outline Your career Your career</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>https://www.google.com/about/careers/applications/jobs/dashboard</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>9c4fdfe4b0423dea9be2</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>7b5b733417ee9a0b9b72</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Recommended jobs</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>https://www.google.com/about/careers/applications/jobs/jobs/recommendations</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>d47f036e91e6d31e4f7d</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>4fbdbd7c924215824d2d</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Saved jobs</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>https://www.google.com/about/careers/applications/jobs/jobs/saved</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>1110ad3f36250b22c236</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>8ef0983d47921ddbf001</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Job alerts</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>https://www.google.com/about/careers/applications/jobs/jobs/alerts</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>4442bc3c0308c3fa5a56</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>819519f7d063bf84b530</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Job categories</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>https://www.amazon.jobs/en/job_categories</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>e092058adcad5d087b91</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>81c7ce581ccc01ad6633</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Job Categories</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>https://www.amazon.jobs/content/en/job-categories</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>78a30a9a9b457e6a6152</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>1c2717338928d9c3c545</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Military careers</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>https://www.amazon.jobs/content/en/career-programs/military</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>cd37c7d05004a553145c</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>6b1aca4a3f26554865a3</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>AWS</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>AWS Pricing Calculator Estimate the cost for your architecture solution</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>https://calculator.aws/?nc2=h_pr_calc</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>dfcb30c1ba2fc02d22a6</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>bd27e452306f8c3d8dc9</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>AWS</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Architecture Center</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/architecture/?nc1=f_cc</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fc315f3e038beb36ce1d</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>82c504586e3fdbc2d2ec</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>AWS</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Analyst Reports</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/resources/analyst-reports/?nc1=f_cc</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>803920c5fd532030cad1</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>3f209db711c2a8e93ebe</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Oracle</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Career Development</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>https://www.oracle.com/careers/life-at-oracle/training/</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>8304754b2065d4478f76</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>41982c192d44c51eb594</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Oracle</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Engineering and Development</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>https://www.oracle.com/careers/opportunities/engineering-development/</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>87307797ce0cda6b7d0f</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>cddc4f6fff5eb9e7a6e9</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Oracle</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Security Clearance Jobs</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>https://www.oracle.com/careers/opportunities/security-clearance-jobs-onsr/</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>be8976ecfb2be0d869b8</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>04fcb77c15ee62895011</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Oracle</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Development and Engineering</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>https://www.oracle.com/careers/students-grads/development-engineering/</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>f9620b6e9de3dd25efa1</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>eb8687f02759dcac1afb</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Oracle</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Internships</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>https://www.oracle.com/careers/students-grads/internships/</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>17cab60649b3db8b4a2d</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>07ab9ff37da4b6ce9e3f</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Oracle</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Search all jobs</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>https://careers.oracle.com/en/sites/jobsearch/jobs?keyword=Engineering%20and%20Development&amp;location=United%20States&amp;locationId=300000000149325</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>03ff8be1852f015ea98f</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>465f1da5ae202191a110</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Oracle</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Cloud Development Engineer</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>https://careers.oracle.com/en/sites/jobsearch/jobs?keyword=Cloud%20Development%20Engineer&amp;location=United%20States&amp;locationId=300000000149325</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>8baed48a71be895c5ddd</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>d21df0b3cc8ee1853d38</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Oracle</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>User Experience Developer</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>https://careers.oracle.com/en/sites/jobsearch/jobs?keyword=User%20Experience%20Developer&amp;location=United%20States&amp;locationId=300000000149325</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>23d4c68cb07a69532389</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ea727cfe696841aa3edf</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Oracle</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>https://careers.oracle.com/en/sites/jobsearch/jobs?keyword=Software%20Engineer&amp;location=United%20States&amp;locationId=300000000149325</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>9a55c6d446a7838dea8c</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
+        <v>35</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>role:Software Engineer</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>cdfe87ab40776e482908</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Oracle</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Product Manager</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>https://careers.oracle.com/en/sites/jobsearch/jobs?keyword=Product%20Manager&amp;location=United%20States&amp;locationId=300000000149325</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>ca0b957d28fe745eb67d</t>
+        </is>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>c25c6f45361950fcddd8</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Oracle</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>https://careers.oracle.com/en/sites/jobsearch/jobs?keyword=Data%20Scientist&amp;location=United%20States&amp;locationId=300000000149325</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>19bb55ce5223696744a1</t>
+        </is>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>859f05b57411db6ee433</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Oracle</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Applications Developer</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>https://careers.oracle.com/en/sites/jobsearch/jobs?keyword=applications%20developer&amp;location=United%20States&amp;locationId=300000000149325</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>45e8077ca8a48500cbe5</t>
+        </is>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>91823d546e634f817cb6</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Oracle</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Hardware Developer</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>https://careers.oracle.com/en/sites/jobsearch/jobs?keyword=Hardware%20developer&amp;location=United%20States&amp;locationId=300000000149325</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>cacb8a125db336ef8806</t>
+        </is>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>6883e903865d8ed4eac3</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Oracle</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Search jobs at Oracle</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>https://careers.oracle.com/en/sites/jobsearch/jobs?location=United%20States&amp;locationId=300000000149325</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>8ff90322b62aa230aa37</t>
+        </is>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>6b3c4856471febc7c1e9</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Oracle</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Careers</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>https://www.oracle.com/corporate/careers/</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>5f5174cbed50d59d066b</t>
+        </is>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>8a07b2dd32b6efeed5ae</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Atlassian</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Rovo Dev Agentic AI for developers</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>https://www.atlassian.com/software/rovo-dev</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>60d0333bbd3c2b7fcc43</t>
+        </is>
+      </c>
+      <c r="K34" t="n">
+        <v>6</v>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>skill:Agentic AI</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>77b8fae331ad75761777</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Atlassian</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Developer support</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>https://developer.atlassian.com/</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>4897cb7e5379415a4d17</t>
+        </is>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>9fc6f8385ec1dd1b6d0e</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Atlassian</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Careers</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>https://www.atlassian.com/company/careers</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>5f5174cbed50d59d066b</t>
+        </is>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>c18d2c5d3c2c9d9c00a9</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Atlassian</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Browse Jobs</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>https://www.atlassian.com/company/careers/all-jobs</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>0fdb2cc581bdff113ffc</t>
+        </is>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>c6c9ac405187719e2fb7</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Atlassian</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>https://www.atlassian.com/company/careers/engineering</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>db1010961b78b74ff4b6</t>
+        </is>
+      </c>
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>9ae59c190ef53c7cf548</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Atlassian</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Early Careers</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>https://www.atlassian.com/company/careers/earlycareers</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>3c6b97d6c3b442e6ddee</t>
+        </is>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>c362578edbdda49d5c74</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Atlassian</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Career Growth</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>https://www.atlassian.com/company/careers/resources/career-growth</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>f07f75a1040133b6d9cc</t>
+        </is>
+      </c>
+      <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>abc00f3fd2272be95dcd</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Adobe</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Search jobs</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>https://careers.adobe.com/us/en/c/engineering-and-product-jobs</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>ec6602ed610da7b838e5</t>
+        </is>
+      </c>
+      <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>c9b42a9d6fc472385747</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Adobe</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Search jobs</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>https://careers.adobe.com/us/en/c/design-jobs</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>ec6602ed610da7b838e5</t>
+        </is>
+      </c>
+      <c r="K42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>44e2f0a02fe4c52481f1</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Adobe</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Search jobs</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>https://careers.adobe.com/us/en/c/research-jobs</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>ec6602ed610da7b838e5</t>
+        </is>
+      </c>
+      <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>c7fc7692a9de464e429a</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Adobe</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Search jobs</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>https://careers.adobe.com/us/en/c/sales-jobs</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>ec6602ed610da7b838e5</t>
+        </is>
+      </c>
+      <c r="K44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>9926a89807cabaa53dd4</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Adobe</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Search jobs</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>https://careers.adobe.com/us/en/c/marketing-and-strategy-jobs</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>ec6602ed610da7b838e5</t>
+        </is>
+      </c>
+      <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>6a7bcc1383e1c79b2845</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Adobe</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Search jobs</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>https://careers.adobe.com/us/en/c/finance-and-operations-jobs</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>ec6602ed610da7b838e5</t>
+        </is>
+      </c>
+      <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>3fb0ab6df7e2d6352d56</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Adobe</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Experience Manager</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>https://business.adobe.com/products/experience-manager/adobe-experience-manager.html</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>fc7547ec4b1bf62571a5</t>
+        </is>
+      </c>
+      <c r="K47" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>cdb954ca4bc94d1533ab</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Adobe</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Adobe Developer</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>https://developer.adobe.com/</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>83a90f01bf2c8bc5e027</t>
+        </is>
+      </c>
+      <c r="K48" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>b4e7c271814b238a2152</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Adobe</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Careers</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>https://www.adobe.com/careers.html</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>5f5174cbed50d59d066b</t>
+        </is>
+      </c>
+      <c r="K49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>6a12a169547f28beeb9b</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Grace CPU Architecture for data centers that transform data into intelligence</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>https://www.nvidia.com/en-us/data-center/grace-cpu/</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>bdf2baf2a1891d5d448a</t>
+        </is>
+      </c>
+      <c r="K50" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>09a3a2b3c243b748a338</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>API Catalog Explore NVIDIA's AI models, blueprints, and tools for developers</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>https://build.nvidia.com/explore/discover</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>768276f63b8a1f38d987</t>
+        </is>
+      </c>
+      <c r="K51" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>1ea87fad60031f94fe59</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Nsight Explore NVIDIA developer tools for AI, graphics, and HPC</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>https://developer.nvidia.com/tools-overview</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>5dc1d87e3bf0ca0b8e5f</t>
+        </is>
+      </c>
+      <c r="K52" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>904e18f9647f812b35f2</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Desktop Manager Enhance multi-display productivity with NVIDIA RTX Desktop Manager</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>https://www.nvidia.com/en-us/software/rtx-desktop-manager/</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>fb43f045f5d1e635f337</t>
+        </is>
+      </c>
+      <c r="K53" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>b1f771b026b7387d9041</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>RTX Accelerated Creative Apps Creative tools and AI-powered apps for artists and designers</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>https://www.nvidia.com/en-us/studio/creative-apps/</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>071b0ee7e0e981665cf4</t>
+        </is>
+      </c>
+      <c r="K54" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>b3a40707029cce4fa4c2</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Computer Aided-Engineering Develop real-time interactive design using AI-accelerated real-time digital twins</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>https://www.nvidia.com/en-us/solutions/cae/</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>7cddf1a4580c66957a8b</t>
+        </is>
+      </c>
+      <c r="K55" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>4da845849f4a97a8bdec</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Reference Architecture Enables vehicles to be L4-ready</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>https://www.nvidia.com/en-us/solutions/autonomous-vehicles/drive-hyperion/</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>4184d1abf3a53a2dcdf6</t>
+        </is>
+      </c>
+      <c r="K56" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>007087dc64d73cc6cb42</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Architecture, Engineering, Construction &amp; Operations</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>https://www.nvidia.com/en-us/industries/aec/</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>fe32a8135649a57b189a</t>
+        </is>
+      </c>
+      <c r="K57" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>41cb7fdc513083e097b4</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Careers</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>https://www.nvidia.com/en-us/about-nvidia/careers/</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>5f5174cbed50d59d066b</t>
+        </is>
+      </c>
+      <c r="K58" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>12a31aeff33beec87603</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Careers</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>https://www.nvidia.com/en-us/about-nvidia/careers/#careers</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>5f5174cbed50d59d066b</t>
+        </is>
+      </c>
+      <c r="K59" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>c11bf57bbe5f8e3a605d</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Find Your Next Job</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>https://jobs.nvidia.com/careers</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>e41561570c5d0d2c52c2</t>
+        </is>
+      </c>
+      <c r="K60" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>f5d2f9301df12777c3f1</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Developers</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>https://developer.nvidia.com/</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>64f840213d90e978976f</t>
+        </is>
+      </c>
+      <c r="K61" t="n">
+        <v>0</v>
+      </c>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>afc835ca36aecfb040f7</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Careers</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>https://www.amd.com/en/corporate/careers.html</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>5f5174cbed50d59d066b</t>
+        </is>
+      </c>
+      <c r="K62" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>21ef72f9e1ba1130bde2</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>https://careers.amd.com/jobs?categories=Engineering&amp;page=1</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>db1010961b78b74ff4b6</t>
+        </is>
+      </c>
+      <c r="K63" t="n">
+        <v>0</v>
+      </c>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>511cddd1f66651af7386</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Developers</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@AMDDevCentral</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>64f840213d90e978976f</t>
+        </is>
+      </c>
+      <c r="K64" t="n">
+        <v>0</v>
+      </c>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>5cdcba49ea66f5d7ef8f</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Developers</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>https://discord.com/invite/amd-dev</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>64f840213d90e978976f</t>
+        </is>
+      </c>
+      <c r="K65" t="n">
+        <v>0</v>
+      </c>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>aea658d9f71565506e0f</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Developer Central</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>https://www.amd.com/en/developer.html</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>14b2c8d1b9e41f037f4d</t>
+        </is>
+      </c>
+      <c r="K66" t="n">
+        <v>0</v>
+      </c>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>b34be13b40b33491ea76</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>ServiceNow</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Careers</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>https://careers.servicenow.com/</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>5f5174cbed50d59d066b</t>
+        </is>
+      </c>
+      <c r="K67" t="n">
+        <v>0</v>
+      </c>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>d08940c1cf2b730e3610</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>ServiceNow</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Jobs</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>https://careers.servicenow.com/jobs/</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>edf25ad40c84573bc420</t>
+        </is>
+      </c>
+      <c r="K68" t="n">
+        <v>0</v>
+      </c>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>95f089d47a6e09dc965c</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>ServiceNow</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>AI, Engineering, &amp; Product</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>https://careers.servicenow.com/teams/ai-engineering-product/</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>4e6e00e32164a7a89471</t>
+        </is>
+      </c>
+      <c r="K69" t="n">
+        <v>0</v>
+      </c>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>6b1ef3c718dd24024b65</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>ServiceNow</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Early Careers</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>https://careers.servicenow.com/early-careers/</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>3c6b97d6c3b442e6ddee</t>
+        </is>
+      </c>
+      <c r="K70" t="n">
+        <v>0</v>
+      </c>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>d14c2e80e991d733ae04</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>ServiceNow</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Saved Jobs 0</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>https://careers.servicenow.com/jobs/saved-jobs/</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>444764ada47ad4eea49d</t>
+        </is>
+      </c>
+      <c r="K71" t="n">
+        <v>0</v>
+      </c>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>c6100ea627606992069e</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Salesforce</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Search jobs</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>https://www.salesforce.com/company/careers/jobs</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>ec6602ed610da7b838e5</t>
+        </is>
+      </c>
+      <c r="K72" t="n">
+        <v>0</v>
+      </c>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>022a5987d0aa6684e12c</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Red Hat</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Red Hat Certified System Administrator exam</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>https://www.redhat.com/en/services/training/ex200-red-hat-certified-system-administrator-rhcsa-exam</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>17f0c2abe5e8da737a4d</t>
+        </is>
+      </c>
+      <c r="K73" t="n">
+        <v>0</v>
+      </c>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>9c115756a4c721899c45</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Red Hat</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Red Hat Certified Engineer exam</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>https://www.redhat.com/en/services/training/ex294-red-hat-certified-engineer-rhce-exam-red-hat-enterprise-linux</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>272012a441ec1c2f4964</t>
+        </is>
+      </c>
+      <c r="K74" t="n">
+        <v>0</v>
+      </c>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1315e089a67efe5c6f7f</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Red Hat</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Red Hat Certified OpenShift Administrator exam</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>https://www.redhat.com/en/services/training/red-hat-certified-openshift-administrator-exam</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>d18c5f93c040172543de</t>
+        </is>
+      </c>
+      <c r="K75" t="n">
+        <v>0</v>
+      </c>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>c759229c2ffd43d9b28b</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Red Hat</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>For developers</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>https://developers.redhat.com/</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>1be795a0660f4d73209e</t>
+        </is>
+      </c>
+      <c r="K76" t="n">
+        <v>0</v>
+      </c>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>6800d2da6befcebf0aa4</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Red Hat</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>See Red Hat jobs</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>https://www.redhat.com/en/jobs</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>947810bec8a2f879cabb</t>
+        </is>
+      </c>
+      <c r="K77" t="n">
+        <v>0</v>
+      </c>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>f7ee9ce3d271bcd8e64a</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Red Hat</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Architecture center</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>https://www.redhat.com/architect/portfolio/</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>97b52e806977db84e18e</t>
+        </is>
+      </c>
+      <c r="K78" t="n">
+        <v>0</v>
+      </c>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2b85c0e6fee12f03abea</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Red Hat</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Search all Red Hat jobs</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>https://redhat.wd5.myworkdayjobs.com/jobs/</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>9c9f5b90894c30d0056e</t>
+        </is>
+      </c>
+      <c r="K79" t="n">
+        <v>0</v>
+      </c>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>885bea62d8d337c8947f</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Red Hat</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>View all job areas</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>https://www.redhat.com/en/jobs/departments</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>208012deec4114cc84b1</t>
+        </is>
+      </c>
+      <c r="K80" t="n">
+        <v>0</v>
+      </c>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>f7508dc1fa4b1fd8efb6</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Red Hat</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Analyst relations</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>https://www.redhat.com/en/about/analysts</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>78e7df790dd32bfc57e5</t>
+        </is>
+      </c>
+      <c r="K81" t="n">
+        <v>0</v>
+      </c>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>0dc36d2bc706a5e58429</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>IBM</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Search Jobs</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>https://www.ibm.com/careers/search</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>acc64b7876a961d2daf4</t>
+        </is>
+      </c>
+      <c r="K82" t="n">
+        <v>0</v>
+      </c>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>ea1b315646d226a29027</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>IBM</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Explore our Career Areas</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>https://www.ibm.com/careers/areas</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>88718b9aceaa73036999</t>
+        </is>
+      </c>
+      <c r="K83" t="n">
+        <v>0</v>
+      </c>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>56a5285e130136ec4db2</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>IBM</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Explore our Careers Blog</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>https://www.ibm.com/careers/blog</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>a50fd85c313fda3e6650</t>
+        </is>
+      </c>
+      <c r="K84" t="n">
+        <v>0</v>
+      </c>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>4ef5d2da6509b35be5cc</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>IBM</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Turn on Job Alerts</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>https://careers.ibm.com/en_US/careers/JobAlerts?source=WEB_Search_NA</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>0292cc871979e3f50282</t>
+        </is>
+      </c>
+      <c r="K85" t="n">
+        <v>0</v>
+      </c>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>cba6c3d9424cf6d62a0f</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>HPE</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Search jobs</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>https://careers.hpe.com/us/en/search-results</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>ec6602ed610da7b838e5</t>
+        </is>
+      </c>
+      <c r="K86" t="n">
+        <v>0</v>
+      </c>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>379eef0eb0f5ea83565c</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Siemens</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Job Search</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>https://jobs.siemens.com/en_US/externaljobs/Home</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>9d10ecb982353730ca28</t>
+        </is>
+      </c>
+      <c r="K87" t="n">
+        <v>0</v>
+      </c>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>0b90edc2c56eac42d654</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Siemens</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>All Jobs</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>https://jobs.siemens.com/en_US/externaljobs/SearchJobs</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>2f60705fd281077a7fcf</t>
+        </is>
+      </c>
+      <c r="K88" t="n">
+        <v>0</v>
+      </c>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>c24f6246c9380d8593fe</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Wipro</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Careers</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>https://careers.wipro.com</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>5f5174cbed50d59d066b</t>
+        </is>
+      </c>
+      <c r="K89" t="n">
+        <v>0</v>
+      </c>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>db55a28cd656e3d76bb1</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Wipro</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Early Careers</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>https://careers.wipro.com/content/Early-Careers/?locale=en_US</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>3c6b97d6c3b442e6ddee</t>
+        </is>
+      </c>
+      <c r="K90" t="n">
+        <v>0</v>
+      </c>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>e685f094729e560f3e62</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Wipro</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Please visit our Job Search page to explore available opportunities in an accessible format.</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr"/>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>https://careers.wipro.com/search/</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>ae9a055445dbf67f8fc8</t>
+        </is>
+      </c>
+      <c r="K91" t="n">
+        <v>0</v>
+      </c>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2457a7fd425839a66a6f</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Wipro</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Search Jobs</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="inlineStr"/>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>https://careers.wipro.com/search</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>acc64b7876a961d2daf4</t>
+        </is>
+      </c>
+      <c r="K92" t="n">
+        <v>0</v>
+      </c>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>b4960e5c288df6bdd122</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Digital Engineering and Manufacturing</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr"/>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>https://www.accenture.com/in-en/services/digital-engineering-manufacturing</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>38328bd3e8425c334b69</t>
+        </is>
+      </c>
+      <c r="K93" t="n">
+        <v>0</v>
+      </c>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>521e382dac65deb4c777</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Industry Analyst Recognition</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr"/>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>https://www.accenture.com/in-en/about/company/industry-analyst</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>39f45bec26a3bf27f63b</t>
+        </is>
+      </c>
+      <c r="K94" t="n">
+        <v>0</v>
+      </c>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>1b6072b81488527110cd</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Search for jobs</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr"/>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>https://www.accenture.com/in-en/careers/jobsearch</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>e61db66cb1cb9ab4a707</t>
+        </is>
+      </c>
+      <c r="K95" t="n">
+        <v>0</v>
+      </c>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>e301f981a761293f7723</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Career areas</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr"/>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>https://www.accenture.com/in-en/careers/explore-careers/career-areas</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>5e848e24718b22ccca16</t>
+        </is>
+      </c>
+      <c r="K96" t="n">
+        <v>0</v>
+      </c>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>bff6ea9fc6a94a2b8e61</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Careers blog</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr"/>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>https://www.accenture.com/in-en/blogs/blogs-careers</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>d2997639bd7459153a1d</t>
+        </is>
+      </c>
+      <c r="K97" t="n">
+        <v>0</v>
+      </c>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>144bb0bb59847da488ad</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Careers</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr"/>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>https://www.accenture.com/us-en/careers</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>5f5174cbed50d59d066b</t>
+        </is>
+      </c>
+      <c r="K98" t="n">
+        <v>0</v>
+      </c>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>c2887af97e2b879a7855</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Careers</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr"/>
+      <c r="E99" t="inlineStr"/>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>https://www.accenture.com/in-en/careers</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>5f5174cbed50d59d066b</t>
+        </is>
+      </c>
+      <c r="K99" t="n">
+        <v>0</v>
+      </c>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>40db937ebddafad87b57</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Saved Jobs</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr"/>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>https://www.accenture.com/in-en/careers/saved-jobs</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>9fca7fb3fb2372f9c6cb</t>
+        </is>
+      </c>
+      <c r="K100" t="n">
+        <v>0</v>
+      </c>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>d46d7b703f78decbe39a</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Explore Digital engineering and manufacturing</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr"/>
+      <c r="E101" t="inlineStr"/>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>https://www.accenture.com/in-en/careers/explore-careers/area-of-interest/engineering-manufacturing-careers</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>9c541c78ff579b7a289c</t>
+        </is>
+      </c>
+      <c r="K101" t="n">
+        <v>0</v>
+      </c>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>3c18984494b52b5e12da</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Early career professionals</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" t="inlineStr"/>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>https://www.accenture.com/in-en/careers/life-at-accenture/entry-level</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>b8886bd249dd01d2d2eb</t>
+        </is>
+      </c>
+      <c r="K102" t="n">
+        <v>0</v>
+      </c>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>d772d2bdc8e354d132d5</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Career Rebooters</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr"/>
+      <c r="E103" t="inlineStr"/>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>https://www.accenture.com/in-en/careers/life-at-accenture/career-reboot-program</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>cd99fb265704b50dec0c</t>
+        </is>
+      </c>
+      <c r="K103" t="n">
+        <v>0</v>
+      </c>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>591898883a3ee11bae65</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Jobs</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" t="inlineStr"/>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>https://careers.cognizant.com/us-en/jobs/</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>edf25ad40c84573bc420</t>
+        </is>
+      </c>
+      <c r="K104" t="n">
+        <v>0</v>
+      </c>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>997a2312f62235400204</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Saved Jobs 0</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" t="inlineStr"/>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>https://careers.cognizant.com/us-en/jobs/saved-jobs/</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>444764ada47ad4eea49d</t>
+        </is>
+      </c>
+      <c r="K105" t="n">
+        <v>0</v>
+      </c>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>c910bf123ece20380db6</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Automation Test Engineer (Selenium/Playwright)</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr"/>
+      <c r="E106" t="inlineStr"/>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>https://careers.cognizant.com/us-en/jobs/00070301082/automation-test-engineer-seleniumplaywright/</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>046698027709f6957569</t>
+        </is>
+      </c>
+      <c r="K106" t="n">
+        <v>0</v>
+      </c>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>6ff0b21bf64c5efa5ac3</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Browse more jobs</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr"/>
+      <c r="E107" t="inlineStr"/>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>https://careers.cognizant.com/us-en/jobs/?orderby=0&amp;pagesize=10&amp;page=1&amp;location=United%20States&amp;radius=100&amp;cname=United%20States&amp;ccode=US</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>a1967626fcbab4884333</t>
+        </is>
+      </c>
+      <c r="K107" t="n">
+        <v>0</v>
+      </c>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>020d0c23217179f50d80</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>HCLTech</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Explore Job Opportunities</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr"/>
+      <c r="E108" t="inlineStr"/>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>https://www.hcltech.com/go/NonTPDemand/9558355/</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>f735f24abe49ffda5865</t>
+        </is>
+      </c>
+      <c r="K108" t="n">
+        <v>0</v>
+      </c>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>cdf001ab831c043286c9</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Careers</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr"/>
+      <c r="E109" t="inlineStr"/>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>https://www.capgemini.com/in-en/careers/</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>5f5174cbed50d59d066b</t>
+        </is>
+      </c>
+      <c r="K109" t="n">
+        <v>0</v>
+      </c>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>e25a7f5ac62859ba0b28</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Career paths</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr"/>
+      <c r="E110" t="inlineStr"/>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>https://www.capgemini.com/in-en/careers/career-paths/</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>9cc9c9304a3d7b68e9d6</t>
+        </is>
+      </c>
+      <c r="K110" t="n">
+        <v>0</v>
+      </c>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>26400c1a620258004d39</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Careers at Capgemini Engineering</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr"/>
+      <c r="E111" t="inlineStr"/>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>https://www.capgemini.com/in-en/careers/career-paths/careers-at-capgemini-engineering/</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>e95856704e988f5eb249</t>
+        </is>
+      </c>
+      <c r="K111" t="n">
+        <v>0</v>
+      </c>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>933f740cdac31f660795</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Careers at Capgemini Invent</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr"/>
+      <c r="E112" t="inlineStr"/>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>https://www.capgemini.com/in-en/careers/career-paths/careers-at-capgemini-invent/</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>98de2e4feb64a6dcf2b4</t>
+        </is>
+      </c>
+      <c r="K112" t="n">
+        <v>0</v>
+      </c>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>b0bac4481e31e223ac2e</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Career events</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr"/>
+      <c r="E113" t="inlineStr"/>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>https://www.capgemini.com/in-en/news/events/?events=upcoming&amp;event-location=&amp;events_type=careers</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>eddc4d3d99da26c95fee</t>
+        </is>
+      </c>
+      <c r="K113" t="n">
+        <v>0</v>
+      </c>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>fa1124a9e5b230a283c1</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Job search</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr"/>
+      <c r="E114" t="inlineStr"/>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>https://www.capgemini.com/in-en/careers/join-capgemini/job-search/</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>86305eccfa35369a37e0</t>
+        </is>
+      </c>
+      <c r="K114" t="n">
+        <v>0</v>
+      </c>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>5f90a1e530edb5fa2b0c</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Analyst recognition</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr"/>
+      <c r="E115" t="inlineStr"/>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>https://www.capgemini.com/in-en/news/analyst-recognition/</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>091ca66bb26d5386b125</t>
+        </is>
+      </c>
+      <c r="K115" t="n">
+        <v>0</v>
+      </c>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>c82a314aac349a74052f</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Explore careers with our brands</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr"/>
+      <c r="E116" t="inlineStr"/>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>https://www.capgemini.com/in-en/about-us/who-we-are/our-brands/</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>9e9c5b3a879ee851121c</t>
+        </is>
+      </c>
+      <c r="K116" t="n">
+        <v>0</v>
+      </c>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>f50b577408e043aed594</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Job offers</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr"/>
+      <c r="E117" t="inlineStr"/>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>https://www.capgemini.com/in-en/careers/join-capgemini/job-search/?country_code=in-en&amp;country_name=India&amp;size=15</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>f18d8e8ebc11a926773a</t>
+        </is>
+      </c>
+      <c r="K117" t="n">
+        <v>0</v>
+      </c>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>9557a3bcba743ae97bd1</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Deloitte India</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Analyst Relations</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr"/>
+      <c r="E118" t="inlineStr"/>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>https://www2.deloitte.com/in/en/about/recognition/analyst-relations/deloitte-analyst-recognitions.html?icid=top_deloitte-analyst-recognitions</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>dbdc5b028ea25d1849d0</t>
+        </is>
+      </c>
+      <c r="K118" t="n">
+        <v>0</v>
+      </c>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>33f8e53fd5f3d107b487</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Deloitte India</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Engineering, AI &amp; Data</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr"/>
+      <c r="E119" t="inlineStr"/>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>https://www2.deloitte.com/in/en/services/consulting/services/engineering-ai-data.html?icid=top_core-business-operations</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>3a9fe80ac4527470fdfe</t>
+        </is>
+      </c>
+      <c r="K119" t="n">
+        <v>0</v>
+      </c>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>bdfb839396f596f504a7</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Deloitte India</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Careers</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr"/>
+      <c r="E120" t="inlineStr"/>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>https://www2.deloitte.com/in/en/careers.html</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>5f5174cbed50d59d066b</t>
+        </is>
+      </c>
+      <c r="K120" t="n">
+        <v>0</v>
+      </c>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>8387ee3bb4a210dc70f8</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Deloitte India</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Job search</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr"/>
+      <c r="E121" t="inlineStr"/>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>https://southasiacareers.deloitte.com/</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>86305eccfa35369a37e0</t>
+        </is>
+      </c>
+      <c r="K121" t="n">
+        <v>0</v>
+      </c>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>496fd86ce041cf39f706</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Deloitte India</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>What to know before you apply Careers</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr"/>
+      <c r="E122" t="inlineStr"/>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>https://www2.deloitte.com/in/en/careers/explore-your-fit/students/terms-disclaimers-recruitment-process.html</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>6d7e4237b0ef817ea3e6</t>
+        </is>
+      </c>
+      <c r="K122" t="n">
+        <v>0</v>
+      </c>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>b61b8faabe0b64279694</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Deloitte India</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>International Tax</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr"/>
+      <c r="E123" t="inlineStr"/>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>https://www2.deloitte.com/in/en/services/tax/services/international-tax.html?icid=top_international-tax</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>50f1adcde6fd9f289672</t>
+        </is>
+      </c>
+      <c r="K123" t="n">
+        <v>0</v>
+      </c>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>0030e67d416eba72d095</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Deloitte India</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr"/>
+      <c r="E124" t="inlineStr"/>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>https://www2.deloitte.com/in/en/services/consulting/services/engineering.html?icid=top_cloud-engineering</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>db1010961b78b74ff4b6</t>
+        </is>
+      </c>
+      <c r="K124" t="n">
+        <v>0</v>
+      </c>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>8c51b98c87e7e839f424</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Deloitte India</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Engineering as a Service/Operate</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr"/>
+      <c r="E125" t="inlineStr"/>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>https://www2.deloitte.com/in/en/what-we-do/capabilities/modern-operate.html?icid=top_modern-operate</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>21f2d5accf8429b3fbcf</t>
+        </is>
+      </c>
+      <c r="K125" t="n">
+        <v>0</v>
+      </c>
+      <c r="L125" t="inlineStr"/>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>8bc3a6aa8140cd790a81</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Deloitte India</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Explore careers</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr"/>
+      <c r="E126" t="inlineStr"/>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>https://www2.deloitte.com/in/en/careers.html?icid=bn_careers</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>e7a6c5d577bfa8588c79</t>
+        </is>
+      </c>
+      <c r="K126" t="n">
+        <v>0</v>
+      </c>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>f21b1f960379ae7e9f24</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>EY</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Careers at EY</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr"/>
+      <c r="E127" t="inlineStr"/>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>https://www.ey.com/en_gl/careers</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>8f22c6abe59e64c0aecb</t>
+        </is>
+      </c>
+      <c r="K127" t="n">
+        <v>0</v>
+      </c>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>0279df473a7b51cc4f28</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>EY</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Job search</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr"/>
+      <c r="E128" t="inlineStr"/>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>https://careers.ey.com</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>86305eccfa35369a37e0</t>
+        </is>
+      </c>
+      <c r="K128" t="n">
+        <v>0</v>
+      </c>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>abf5db7f9a8e47f33b0f</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>EY</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Early careers</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr"/>
+      <c r="E129" t="inlineStr"/>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>https://eyglobal.yello.co/job_boards/c1riT--B2O-KySgYWsZO1Q</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>f22b8996984ca5998a5d</t>
+        </is>
+      </c>
+      <c r="K129" t="n">
+        <v>0</v>
+      </c>
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>532b63c5276b67ed1bd3</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>EY</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Find jobs</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr"/>
+      <c r="E130" t="inlineStr"/>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>https://careers.ey.com/ey/search/?createNewAlert=false&amp;q=&amp;locationsearch=&amp;optionsFacetsDD_country=&amp;optionsFacetsDD_customfield1=&amp;locale=en_US</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>8b467dd5f0d2ad132ed1</t>
+        </is>
+      </c>
+      <c r="K130" t="n">
+        <v>0</v>
+      </c>
+      <c r="L130" t="inlineStr"/>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>692e1cc3283b51d1983e</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>PwC India</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Careers</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr"/>
+      <c r="E131" t="inlineStr"/>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>https://www.pwc.in/careers.html</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>5f5174cbed50d59d066b</t>
+        </is>
+      </c>
+      <c r="K131" t="n">
+        <v>0</v>
+      </c>
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>f67d75af7220913c1e02</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>PwC India</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Digital Engineering and Manufacturing</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr"/>
+      <c r="E132" t="inlineStr"/>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>https://www.pwc.in/digital-engineering-and-manufacturing.html</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>38328bd3e8425c334b69</t>
+        </is>
+      </c>
+      <c r="K132" t="n">
+        <v>0</v>
+      </c>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>6fec8b402832e1f911b6</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>PwC India</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Internet Access and Internet Advertising</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr"/>
+      <c r="E133" t="inlineStr"/>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>https://www.pwc.in/industries/entertainment-and-media/internet-access-and-internet-advertising.html</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>136c6bd8e1aed73e89c1</t>
+        </is>
+      </c>
+      <c r="K133" t="n">
+        <v>0</v>
+      </c>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>5cbf84d639c364d628c7</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>PwC India</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>International Business Groups</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr"/>
+      <c r="E134" t="inlineStr"/>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>https://www.pwc.in/services/international-business-groups.html</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>c786b09b2e3b6fbedc4c</t>
+        </is>
+      </c>
+      <c r="K134" t="n">
+        <v>0</v>
+      </c>
+      <c r="L134" t="inlineStr"/>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>dce18df8eb4eacfa55ae</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>PwC India</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Analyst relations</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr"/>
+      <c r="E135" t="inlineStr"/>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>https://www.pwc.com/gx/en/about/analyst-relations.html</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>78e7df790dd32bfc57e5</t>
+        </is>
+      </c>
+      <c r="K135" t="n">
+        <v>0</v>
+      </c>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>63d8a8e1eb83ae6dfccb</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>PwC India</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Campus Careers</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr"/>
+      <c r="E136" t="inlineStr"/>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>https://www.pwc.in/careers/campus-careers.html</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>65453aadb0760daefaa9</t>
+        </is>
+      </c>
+      <c r="K136" t="n">
+        <v>0</v>
+      </c>
+      <c r="L136" t="inlineStr"/>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>834ae2eac170d71459a4</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>PwC India</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Find your next career opportunity</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr"/>
+      <c r="E137" t="inlineStr"/>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>https://www.pwc.in/careers/experienced-jobs.html</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>2aff8920114db8604297</t>
+        </is>
+      </c>
+      <c r="K137" t="n">
+        <v>0</v>
+      </c>
+      <c r="L137" t="inlineStr"/>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>4a5411e6891b6edefa11</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>PwC India</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Grow your career with PwC</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr"/>
+      <c r="E138" t="inlineStr"/>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>https://www.pwc.in/careers.html#territory-selector</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>57f9a3b56c05ffb975ef</t>
+        </is>
+      </c>
+      <c r="K138" t="n">
+        <v>0</v>
+      </c>
+      <c r="L138" t="inlineStr"/>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>d557c188155263dabf02</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>PwC India</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Meet Shruti A civil engineer can become a marketeer! Learn more</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr"/>
+      <c r="E139" t="inlineStr"/>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>https://www.pwc.in/careers/shruti-kumar.html</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>28837117881843d5df40</t>
+        </is>
+      </c>
+      <c r="K139" t="n">
+        <v>0</v>
+      </c>
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>c3188d53a31d072a6ea9</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>PwC India</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Meet Bindiya I love my kids. I love my job. I love PwC. Learn more</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr"/>
+      <c r="E140" t="inlineStr"/>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>https://www.pwc.in/careers/meet-bindiya.html</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>d79aa33e8de56b508c3d</t>
+        </is>
+      </c>
+      <c r="K140" t="n">
+        <v>0</v>
+      </c>
+      <c r="L140" t="inlineStr"/>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>701f88f9186c8dd4321f</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>PwC India</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Find your career at PwC</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr"/>
+      <c r="E141" t="inlineStr"/>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>https://www.pwc.in/careers/job-search.html</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>b28bc4df21f516db779c</t>
+        </is>
+      </c>
+      <c r="K141" t="n">
+        <v>0</v>
+      </c>
+      <c r="L141" t="inlineStr"/>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>f20a62988e13e7ab3862</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>KPMG India</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Corporate and international tax</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr"/>
+      <c r="E142" t="inlineStr"/>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>https://kpmg.com/in/en/services/tax/international-tax.html</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>5e1f1608cf454b660a3c</t>
+        </is>
+      </c>
+      <c r="K142" t="n">
+        <v>0</v>
+      </c>
+      <c r="L142" t="inlineStr"/>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>d1a38d15dcf4e2595e41</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>KPMG India</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Careers</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr"/>
+      <c r="E143" t="inlineStr"/>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>https://kpmg.com/in/en/careers.html</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>5f5174cbed50d59d066b</t>
+        </is>
+      </c>
+      <c r="K143" t="n">
+        <v>0</v>
+      </c>
+      <c r="L143" t="inlineStr"/>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>8db437c725c2b0b9d209</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>KPMG India</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>KPMG International hotline</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr"/>
+      <c r="E144" t="inlineStr"/>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>https://kpmg.com/xx/en/about/kpmg-international-hotline.html</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>203c735dcc289c11b5c8</t>
+        </is>
+      </c>
+      <c r="K144" t="n">
+        <v>0</v>
+      </c>
+      <c r="L144" t="inlineStr"/>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>c61b48cb7b4953b8623c</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Freshworks</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Explore jobs</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr"/>
+      <c r="E145" t="inlineStr"/>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>https://careers.smartrecruiters.com/Freshworks</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>a2ca9b483d68e976de19</t>
+        </is>
+      </c>
+      <c r="K145" t="n">
+        <v>0</v>
+      </c>
+      <c r="L145" t="inlineStr"/>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>bece5a21df011de5c279</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Freshworks</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Careers</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr"/>
+      <c r="E146" t="inlineStr"/>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>https://www.freshworks.com/company/careers/</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>5f5174cbed50d59d066b</t>
+        </is>
+      </c>
+      <c r="K146" t="n">
+        <v>0</v>
+      </c>
+      <c r="L146" t="inlineStr"/>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>01b98718d9f86be09e90</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Flipkart</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Explore Jobs and Teams â</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr"/>
+      <c r="E147" t="inlineStr"/>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>https://flipkart.turbohire.co/careerpage/4d757ba0-3d57-448a-b82c-238ed87ac90f</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>43e1035eef9413a8ac72</t>
+        </is>
+      </c>
+      <c r="K147" t="n">
+        <v>0</v>
+      </c>
+      <c r="L147" t="inlineStr"/>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>3d73a7b3adf0bacb6a40</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>S&amp;P Global</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Careers</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr"/>
+      <c r="E148" t="inlineStr"/>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>https://careers.spglobal.com#headerNavFour</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>5f5174cbed50d59d066b</t>
+        </is>
+      </c>
+      <c r="K148" t="n">
+        <v>0</v>
+      </c>
+      <c r="L148" t="inlineStr"/>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>afbdb79ede2ebfebe255</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>S&amp;P Global</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Search for a Job</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr"/>
+      <c r="E149" t="inlineStr"/>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>https://careers.spglobal.com/jobs</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>571cc513a61e0823ca8d</t>
+        </is>
+      </c>
+      <c r="K149" t="n">
+        <v>0</v>
+      </c>
+      <c r="L149" t="inlineStr"/>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>de14d6d2f28c3f3f7581</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>S&amp;P Global</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Careers</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr"/>
+      <c r="E150" t="inlineStr"/>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>https://www.spglobal.com/en/careers/</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>5f5174cbed50d59d066b</t>
+        </is>
+      </c>
+      <c r="K150" t="n">
+        <v>0</v>
+      </c>
+      <c r="L150" t="inlineStr"/>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>059b44a4b5945b2fdaf0</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Persistent Systems</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Software Product Engineering</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr"/>
+      <c r="E151" t="inlineStr"/>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>https://www.persistent.com/services/software-product-engineering/</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>6cc18d1345e617ef414c</t>
+        </is>
+      </c>
+      <c r="K151" t="n">
+        <v>0</v>
+      </c>
+      <c r="L151" t="inlineStr"/>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>fcbe76abb37e0436ee41</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Persistent Systems</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Internet of Things (IoT)</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr"/>
+      <c r="E152" t="inlineStr"/>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>https://marketplace.persistentproducts.com/marketplace/#/storefront/taxonomy?categoryId=31&amp;level1Name=IOT&amp;level2Name=</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>13ef0396f16022dc8072</t>
+        </is>
+      </c>
+      <c r="K152" t="n">
+        <v>0</v>
+      </c>
+      <c r="L152" t="inlineStr"/>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>1a1f6db1fd9cd741752f</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Persistent Systems</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Careers</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr"/>
+      <c r="E153" t="inlineStr"/>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>https://www.persistent.com/careers</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:14:08</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>5f5174cbed50d59d066b</t>
+        </is>
+      </c>
+      <c r="K153" t="n">
+        <v>0</v>
+      </c>
+      <c r="L153" t="inlineStr"/>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O153" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/jobs.xlsx
+++ b/jobs.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-09-02 15:22:08</t>
+          <t>2026-09-03 01:57:07</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">

--- a/jobs.xlsx
+++ b/jobs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:O75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -496,65 +496,5244 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>84dd80f95e06bf82d47e</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ABB</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>This job is with ABB, an inclusive employer and a member of myGwork – the largest global platform for the LGBTQ business community. Please do not contact the recruiter directly. At ABB, we help industries run leaner and cleaner—and every person here makes that happen. You’ll be empowered to lead, su</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/land/ad/5852164535?se=7N2EH0en8RG9XvIMYZlJjg&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=9209E8787944C1DC2369EB9C41C3094786ECA2A0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>a8549fb9aa5c3b8b80bd</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>45</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>role:Software Engineer, location:Bangalore</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>6539152bda7af9ffaf90</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ABB</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Associate Software Engineer</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>This job is with ABB, an inclusive employer and a member of myGwork – the largest global platform for the LGBTQ business community. Please do not contact the recruiter directly. At ABB, we help industries run leaner and cleaner—and every person here makes that happen. You’ll be empowered to lead, su</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/land/ad/5841509341?se=7N2EH0en8RG9XvIMYZlJjg&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=D1270B04110BECC323487E81E9C4D66C691C4651</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>bf51982a8304bbb219b1</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>53</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>role:Software Engineer, location:Bangalore, experience:associate</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>dce1fa2e8599cda3aaa0</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Moody's</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Staff Software Engineer</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>This job is with Moody's, an inclusive employer and a member of myGwork – the largest global platform for the LGBTQ business community. Please do not contact the recruiter directly. At Moody's, we unite the brightest minds to turn today’s risks into tomorrow’s opportunities. We do this by striving t</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/land/ad/5846723030?se=7N2EH0en8RG9XvIMYZlJjg&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=A12DF7C02E8D43AB5777E0856BEFF63ACAB7EB16</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>66dc2e5e20f98f9e760e</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>45</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>role:Software Engineer, location:Bangalore</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>0a6e4fb9a2c80fd85bd4</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Moody's</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Staff Software Engineer</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>This job is with Moody's, an inclusive employer and a member of myGwork – the largest global platform for the LGBTQ business community. Please do not contact the recruiter directly. At Moody's, we unite the brightest minds to turn today’s risks into tomorrow’s opportunities. We do this by striving t</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/land/ad/5846723078?se=7N2EH0en8RG9XvIMYZlJjg&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=E4A1A73C5F666ACB84BAE4E1985959AA9FF61296</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>66dc2e5e20f98f9e760e</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>45</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>role:Software Engineer, location:Bangalore</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>3307be790c1dce9b1e6d</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Moody's</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Staff Software Engineer</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>This job is with Moody's, an inclusive employer and a member of myGwork – the largest global platform for the LGBTQ business community. Please do not contact the recruiter directly. At Moody's, we unite the brightest minds to turn today’s risks into tomorrow’s opportunities. We do this by striving t</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/land/ad/5846723388?se=7N2EH0en8RG9XvIMYZlJjg&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=43BAAB4C2B9B91025B2C4E2EF1039AF52FAE195C</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>66dc2e5e20f98f9e760e</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>45</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>role:Software Engineer, location:Bangalore</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>8681e23f47443a9cb786</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Warner Bros. Discovery</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Principal Software Engineer</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>This job is with Warner Bros. Discovery, an inclusive employer and a member of myGwork – the largest global platform for the LGBTQ business community. Please do not contact the recruiter directly. Welcome to Warner Bros. Discovery… the stuff dreams are made of. Who We Are… When we say, “the stuff dr</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/land/ad/5837139560?se=7N2EH0en8RG9XvIMYZlJjg&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=EBB55035A79BA2127E934C86759FC4C6036987E2</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>573b1f97252650039b4b</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>45</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>role:Software Engineer, location:Bangalore</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>e3b8102e3d1f4273b8ba</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Moody's</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Staff Software Engineer</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>This job is with Moody's, an inclusive employer and a member of myGwork – the largest global platform for the LGBTQ business community. Please do not contact the recruiter directly. At Moody's, we unite the brightest minds to turn today’s risks into tomorrow’s opportunities. We do this by striving t</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/land/ad/5846723080?se=7N2EH0en8RG9XvIMYZlJjg&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=BDD9C2926EC9D90B80A0CDAE02AC3B622B32FC99</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>66dc2e5e20f98f9e760e</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>45</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>role:Software Engineer, location:Bangalore</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>e983b9a66f969dea17d9</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ABB</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Principal Software Engineer</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>This job is with ABB, an inclusive employer and a member of myGwork – the largest global platform for the LGBTQ business community. Please do not contact the recruiter directly. At ABB, we help industries run leaner and cleaner—and every person here makes that happen. You’ll be empowered to lead, su</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/land/ad/5852164440?se=7N2EH0en8RG9XvIMYZlJjg&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=E6EF3C01409D9B7FBC4F3B6B98E5F1E4B86BAA84</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>820550bbca89260bfdf3</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>45</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>role:Software Engineer, location:Bangalore</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>86ab19a9cec00d6f0ea9</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Arcana</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Software Engineer in Test</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>We are looking for a meticulous SDET who will be responsible for the design and implementation of automated tests and test environments for Arcana. The engineer must have a passion for diving into data and technology, be a problem solver, and have a desire to improve software quality within a team e</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/land/ad/5864426564?se=7N2EH0en8RG9XvIMYZlJjg&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=B290C528C0913CA557D80924BA0AF30FE71A1A00</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>f60431bccffac2a157db</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>45</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>role:Software Engineer, location:Bangalore</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>d0c6ae24b22a2a6a2f72</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Recro</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Software Engineer - Browser Automation</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mission If you ask a hospital today how much a treatment will cost, the answer is usually: “We don’t know.” Not because providers don’t want to tell you but because patient cost is computed across insurance plans, negotiated rates, and billing rules that are fragmented, opaque, and not designed for </t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/land/ad/5864426312?se=7N2EH0en8RG9XvIMYZlJjg&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=A27346080A30C3E564878BC09AB7AD3C017DF8A2</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>bb4229ae4e92fd53fd70</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>45</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>role:Software Engineer, location:Bangalore</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>b8fe94c872364102a694</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Danaher</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Lead Software Engineer: Automation</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>This job is with Danaher, an inclusive employer and a member of myGwork – the largest global platform for the LGBTQ business community. Please do not contact the recruiter directly. Bring more to life. Are you ready to accelerate your potential and make a real difference within life sciences, diagno</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/land/ad/5846723288?se=7N2EH0en8RG9XvIMYZlJjg&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=C7066AF12EC54DA41656ED99F258227EC0DC9B76</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>26e3f604e1f65659c17d</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>45</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>role:Software Engineer, location:Bangalore</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>53ba2c5a57077a241e1a</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Warner Bros. Discovery</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Staff Software Engineer - iOS</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>This job is with Warner Bros. Discovery, an inclusive employer and a member of myGwork – the largest global platform for the LGBTQ business community. Please do not contact the recruiter directly. Welcome to Warner Bros. Discovery… the stuff dreams are made of. Who We Are… When we say, “the stuff dr</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/land/ad/5838614193?se=7N2EH0en8RG9XvIMYZlJjg&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=9A92C6347994E53121C302383944CFFCF637848A</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>6c790a91ce0ffd7dd4b9</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>45</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>role:Software Engineer, location:Bangalore</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>c1b81b6294bf72c8cd98</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Moody's</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Software Engineer - Sharepoint Developer</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>This job is with Moody's, an inclusive employer and a member of myGwork – the largest global platform for the LGBTQ business community. Please do not contact the recruiter directly. At Moody's, we unite the brightest minds to turn today’s risks into tomorrow’s opportunities. We do this by striving t</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/land/ad/5865064890?se=7N2EH0en8RG9XvIMYZlJjg&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=7D08E55F7B8119270271C16BDF7CB0165F3E88A9</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>2bf16fb064685a7ffe3b</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>45</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>role:Software Engineer, location:Bangalore</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>7574fe03b7a6a827ec33</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>eBay</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Software Engineer Streaming/Messaging</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>This job is with eBay, an inclusive employer and a member of myGwork – the largest global platform for the LGBTQ business community. Please do not contact the recruiter directly. At eBay, we're more than a global ecommerce leader - we're changing the way the world shops and sells. Our platform empow</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/land/ad/5857251208?se=7N2EH0en8RG9XvIMYZlJjg&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=D2EDC0229B026B966CEF760E9377E8C7A3A5D261</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fb9977ca338517ea419e</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>45</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>role:Software Engineer, location:Bangalore</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2aa35321d75f6cef4bc5</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Moody's</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Principal Software Engineer - AI</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>This job is with Moody's, an inclusive employer and a member of myGwork – the largest global platform for the LGBTQ business community. Please do not contact the recruiter directly. At Moody's, we unite the brightest minds to turn today’s risks into tomorrow’s opportunities. We do this by striving t</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/land/ad/5847959803?se=7N2EH0en8RG9XvIMYZlJjg&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=24850D9B9C940C34EAB88A822280AD413E8F4422</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>1baeb17e541bd0dce352</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>80</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>role:Software Engineer, role:Software Engineer - AI, location:Bangalore</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>b6a3ccfd29d2b20d8710</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Recro</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Historian System and Software Engineer</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>In this role, you will lead the design, development, and maintenance of scalable enterprise software applications for our Global AI-Smart Operations. If you thrive on solving complex technical challenges, driving CI/CD automation, and working with industrial data streams, we want to hear from you! ️</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/land/ad/5864434547?se=7N2EH0en8RG9XvIMYZlJjg&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=651D2303C08F41D72AF5F39C4E5F39DD317D6233</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>46fdec9cf0f3e22c5bb6</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>45</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>role:Software Engineer, location:Bangalore</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>816aab17b0bc21c31ac9</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Danaher</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Lead Software Engineer -C#, .NET</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>This job is with Danaher, an inclusive employer and a member of myGwork – the largest global platform for the LGBTQ business community. Please do not contact the recruiter directly. Are you ready to accelerate your potential and make a real difference within life sciences, diagnostics and biotechnol</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/land/ad/5846723705?se=7N2EH0en8RG9XvIMYZlJjg&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=0A661A4F070C72B197802638222F80DAA159D65D</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>a697666f372adfebe174</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>45</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>role:Software Engineer, location:Bangalore</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>496465d779d2588ef35d</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Danaher</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Lead Software Engineer (Manual Testing)</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>This job is with Danaher, an inclusive employer and a member of myGwork – the largest global platform for the LGBTQ business community. Please do not contact the recruiter directly. NOTE – Do not use this job posting template for AB Sciex Germany GmbH legal entity jobs. Use the “SCIEX Germany GmbH L</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/land/ad/5846723424?se=7N2EH0en8RG9XvIMYZlJjg&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=5F76D0F35F3A0014DC5915C140484D906CF24167</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>a30e107d632cab9549e7</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>45</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>role:Software Engineer, location:Bangalore</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>9338e7064da1c281f290</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Kyndryl</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Sr. Software Engineer - Backend Java</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>This job is with Kyndryl, an inclusive employer and a member of myGwork – the largest global platform for the LGBTQ business community. Please do not contact the recruiter directly. Who We Are At Kyndryl, we run and reimagine the mission-critical technology systems that drive advantage for the world</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/land/ad/5837138668?se=7N2EH0en8RG9XvIMYZlJjg&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=AE41B534F2371B442102070C83D6AA62C10BF7B4</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>cfde9fd93319b687d92c</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>45</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>role:Software Engineer, location:Bangalore</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>6bc91719843628e92971</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Kyndryl</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Platform Engineer</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>This job is with Kyndryl, an inclusive employer and a member of myGwork – the largest global platform for the LGBTQ business community. Please do not contact the recruiter directly. Who We Are At Kyndryl, we run and reimagine the mission-critical technology systems that drive advantage for the world</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/land/ad/5855007034?se=UifuH0en8RG2HomFYOMXfQ&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=83A2754BAF8C6CCAD9027F1D5977A1C5CB44300B</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>ceca84cf6d2ca557991f</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>45</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>role:Platform Engineer, location:Bangalore</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>dcc269ace9386a724ea6</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Kyndryl</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Platform Engineer - Data</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>This job is with Kyndryl, an inclusive employer and a member of myGwork – the largest global platform for the LGBTQ business community. Please do not contact the recruiter directly. Who We Are At Kyndryl, we run and reimagine the mission-critical technology systems that drive advantage for the world</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/land/ad/5855007050?se=UifuH0en8RG2HomFYOMXfQ&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=C4EED2A519F03E0B87055D11E8D44FFF3C83C9AE</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>0ddef43662b0a513eaff</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>45</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>role:Platform Engineer, location:Bangalore</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>8670c321c7cac5a36180</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Kyndryl</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Platform Engineer - Data</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>This job is with Kyndryl, an inclusive employer and a member of myGwork – the largest global platform for the LGBTQ business community. Please do not contact the recruiter directly. Who We Are At Kyndryl, we run and reimagine the mission-critical technology systems that drive advantage for the world</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/land/ad/5855007011?se=UifuH0en8RG2HomFYOMXfQ&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=2072E1F6EA4EA104D4C5F33605E51A05D7D97600</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>0ddef43662b0a513eaff</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>45</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>role:Platform Engineer, location:Bangalore</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>e440da61e6e9efc402de</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Kyndryl</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>DevOps / Platform Engineer</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>This job is with Kyndryl, an inclusive employer and a member of myGwork – the largest global platform for the LGBTQ business community. Please do not contact the recruiter directly. Who We Are At Kyndryl, we run and reimagine the mission-critical technology systems that drive advantage for the world</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/land/ad/5837139061?se=UifuH0en8RG2HomFYOMXfQ&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=5285674828FE37C646BCC77D46165795A7AC83F3</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>5639a74955a329af8fdb</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>45</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>role:Platform Engineer, location:Bangalore</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>c142cd070332af8aeaba</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>eBay</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>AI Platform Engineer</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>This job is with eBay, an inclusive employer and a member of myGwork – the largest global platform for the LGBTQ business community. Please do not contact the recruiter directly. At eBay, we're more than a global ecommerce leader - we're changing the way the world shops and sells. Our platform empow</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/land/ad/5857982488?se=UifuH0en8RG2HomFYOMXfQ&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=A746E3D6C2072081EB037DB5FF89DB2B1F4A7F7A</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>003a5b09f0f9cab65bcb</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>80</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>role:Platform Engineer, role:AI Platform Engineer, location:Bangalore</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2847d3452a8e75b6dd61</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>eBay</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>AI Platform Engineer</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>This job is with eBay, an inclusive employer and a member of myGwork – the largest global platform for the LGBTQ business community. Please do not contact the recruiter directly. At eBay, we're more than a global ecommerce leader - we're changing the way the world shops and sells. Our platform empow</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/land/ad/5857251116?se=UifuH0en8RG2HomFYOMXfQ&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=08120470A120A602552281268EC24E0672DD8DC2</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>003a5b09f0f9cab65bcb</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>80</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>role:Platform Engineer, role:AI Platform Engineer, location:Bangalore</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>19e6bf640f086b242282</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>eBay</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>AI Platform Engineer</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>This job is with eBay, an inclusive employer and a member of myGwork – the largest global platform for the LGBTQ business community. Please do not contact the recruiter directly. At eBay, we're more than a global ecommerce leader - we're changing the way the world shops and sells. Our platform empow</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/land/ad/5857982562?se=UifuH0en8RG2HomFYOMXfQ&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=D215B0FD12910D6EA0FB670B7E4060E2013251A2</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>003a5b09f0f9cab65bcb</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
+        <v>80</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>role:Platform Engineer, role:AI Platform Engineer, location:Bangalore</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>0da56a893ccd57a7c71f</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Kyndryl</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Lead Azure Platform Engineer</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>This job is with Kyndryl, an inclusive employer and a member of myGwork – the largest global platform for the LGBTQ business community. Please do not contact the recruiter directly. Who We Are At Kyndryl, we run and reimagine the mission-critical technology systems that drive advantage for the world</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/land/ad/5859162464?se=UifuH0en8RG2HomFYOMXfQ&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=59B2F0B23A1BFC07E04BCF89D27E5A35FAEE8526</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>439c745ba867644d178d</t>
+        </is>
+      </c>
+      <c r="K28" t="n">
+        <v>45</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>role:Platform Engineer, location:Bangalore</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>3d1ec91f61eff2feb638</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>eBay</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Sr Platform Engineer, Java Fmwk</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>This job is with eBay, an inclusive employer and a member of myGwork – the largest global platform for the LGBTQ business community. Please do not contact the recruiter directly. At eBay, we're more than a global ecommerce leader - we're changing the way the world shops and sells. Our platform empow</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/land/ad/5857251186?se=UifuH0en8RG2HomFYOMXfQ&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=86E067A84B4608D56A8DF7DAC543EB1D3E73B398</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>aa0e96d98caef2fa536a</t>
+        </is>
+      </c>
+      <c r="K29" t="n">
+        <v>45</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>role:Platform Engineer, location:Bangalore</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>1ea934d0d8a136cffb4f</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Kyndryl</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Sr. Associate Platform Engineering - GCP</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>This job is with Kyndryl, an inclusive employer and a member of myGwork – the largest global platform for the LGBTQ business community. Please do not contact the recruiter directly. Who We Are At Kyndryl, we run and reimagine the mission-critical technology systems that drive advantage for the world</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/land/ad/5837138647?se=UifuH0en8RG2HomFYOMXfQ&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=43FA936716990B9015CD9544611E036309803B15</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>0328ca89ac93ac45b0af</t>
+        </is>
+      </c>
+      <c r="K30" t="n">
+        <v>24</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>skill:Platform Engineering, location:Bangalore, experience:associate</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>11547a5c0203c565e045</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>eBay</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>MTS 2, Software Engineer, Data Platforms</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>This job is with eBay, an inclusive employer and a member of myGwork – the largest global platform for the LGBTQ business community. Please do not contact the recruiter directly. At eBay, we're more than a global ecommerce leader - we're changing the way the world shops and sells. Our platform empow</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/land/ad/5857251152?se=UifuH0en8RG2HomFYOMXfQ&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=F6ED6E5761AAB007E2A108EBC1289F6B09295EAC</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>46cb39c0bc105ab9f28b</t>
+        </is>
+      </c>
+      <c r="K31" t="n">
+        <v>45</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>role:Software Engineer, location:Bangalore</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>8562f85dbab1fd8d54d1</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Licious</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>SDE 2 - Data Engineering</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">At Licious, we are building a scalable and reliable data platform that powers critical business decisions, operational intelligence, and next-generation data products. As an SDE II – Data Platform , you will play a key role in designing, building, and optimizing large-scale distributed data systems </t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/land/ad/5864428229?se=UifuH0en8RG2HomFYOMXfQ&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=99C28A26BE1D494A2F03EEEA91A33DAC3BC3C168</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>fe392e1d4889af626cfa</t>
+        </is>
+      </c>
+      <c r="K32" t="n">
+        <v>57</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>role:SDE, skill:Platform Engineering, skill:Distributed Systems, location:Bangalore</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>79e4c14c7c21dfa3460f</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Kyndryl</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Software Engineer - Microsoft Power Platform Developer</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>This job is with Kyndryl, an inclusive employer and a member of myGwork – the largest global platform for the LGBTQ business community. Please do not contact the recruiter directly. Who We Are At Kyndryl, we run and reimagine the mission-critical technology systems that drive advantage for the world</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/land/ad/5837138735?se=UifuH0en8RG2HomFYOMXfQ&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=30DB8AF6167416207F9C7D2B1D78CA8ED201388F</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>c9d99c912c70ba128422</t>
+        </is>
+      </c>
+      <c r="K33" t="n">
+        <v>45</v>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>role:Software Engineer, location:Bangalore</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>430a97dc73efd447c911</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Kyndryl</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Software Engineer - Microsoft Power Platform Developer</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>This job is with Kyndryl, an inclusive employer and a member of myGwork – the largest global platform for the LGBTQ business community. Please do not contact the recruiter directly. Who We Are At Kyndryl, we run and reimagine the mission-critical technology systems that drive advantage for the world</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/land/ad/5841509246?se=UifuH0en8RG2HomFYOMXfQ&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=77A93A263198B258FF86EBD054D2013BF2EF8C57</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>c9d99c912c70ba128422</t>
+        </is>
+      </c>
+      <c r="K34" t="n">
+        <v>45</v>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>role:Software Engineer, location:Bangalore</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>0086e87f00a0c05643fb</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>People10 Techno Soft</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Platform Engineer</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Indiranagar, Bangalore</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>This is a remote position. Platform Engineer (DevSecOps / AWS / MySQL)@ PEOPLE10 JOB LOCATION : Bangalore, India (Remote) EXPERIENCE : 5–6 Years SHIFT : 4PM -12AM IST Requirement Type :Contract :3-6 Months Role Summary : We are seeking a hands-on Platform Engineer with strong technical execution and</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/details/5855696341?utm_medium=api&amp;utm_source=447522e9</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>cd63374c022fc9ffbc3b</t>
+        </is>
+      </c>
+      <c r="K35" t="n">
+        <v>45</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>role:Platform Engineer, location:Bangalore</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>caf36a9cfd9dd741c544</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>HCLTech</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Excellent opportunity for Big Data Platform Engineer at Chennai/Bangalore. Interested candidates pls email the resume to nirmalajosepin.s@hcltech.com Exp: 8 Yrs Required Skills: Core Big Data Platform Apache Iceberg / Delta Lake / Apache Hudi Apache Airflow (Orchestration) Kubernetes (SKE/AKS /EKS/G</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/land/ad/5864429013?se=UifuH0en8RG2HomFYOMXfQ&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=9A91FBA4E8D876B47567009614F17DD2612A38B8</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>82b4b59b964a0c66c935</t>
+        </is>
+      </c>
+      <c r="K36" t="n">
+        <v>22</v>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>skill:Python, skill:SQL, location:Bangalore</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>7d2a39f1c000bb850899</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Cargill</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Platform Engineer</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Job Purpose and Impact  The Professional, Platform Engineering job maintains and partners to design and develop digital technology infrastructure to support information technology applications and services. With limited supervision, this job collaborates with cross functional teams to implement new </t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/details/5762102181?utm_medium=api&amp;utm_source=447522e9</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>53e355f67c14369bd4de</t>
+        </is>
+      </c>
+      <c r="K37" t="n">
+        <v>51</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>role:Platform Engineer, skill:Platform Engineering, location:Bangalore</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>c3054eda6b6c73b909fb</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>People10 Techno Soft</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Platform Engineer</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Indiranagar, Bangalore</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>This is a remote position. Platform Engineer (DevSecOps / AWS / MySQL)@ PEOPLE10 JOB LOCATION : Bangalore, India (Remote) EXPERIENCE : 5–6 Years SHIFT : 4PM -12AM IST Requirement Type :Contract :3-6 Months Role Summary : We are seeking a hands-on Platform Engineer with strong technical execution and</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/details/5856317467?utm_medium=api&amp;utm_source=447522e9</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>cd63374c022fc9ffbc3b</t>
+        </is>
+      </c>
+      <c r="K38" t="n">
+        <v>45</v>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>role:Platform Engineer, location:Bangalore</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>c2c96007cb3bf6fd4706</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Recrew AI</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Platform Engineer</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Role: Lead - Platform Engineering Function: Platform Engineering / Infrastructure Location: Bengaluru Type: Full-time Industry: Information Technology &amp; Services, Computer Software, Fintech About Company The company is a Bengaluru-based enterprise tech startup founded in 2016. It provides regulatory</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/details/5838096644?utm_medium=api&amp;utm_source=447522e9</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>73f6d3ddc72923768cea</t>
+        </is>
+      </c>
+      <c r="K39" t="n">
+        <v>51</v>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>role:Platform Engineer, skill:Platform Engineering, location:Bangalore</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>0fa3d588c2f7472524a1</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Tekskills India Private Limited</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Platform Engineer</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>We are hiring an experienced Platform Engineer with strong expertise in Cloudera, Kafka, Databricks, Azure Synapse, PySpark, and Infrastructure Automation . Mandatory Skills Cloudera Platform Administration Cloudera Hadoop Administration Kafka Cluster Administration &amp; Maintenance Databricks Apache I</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/details/5804149618?utm_medium=api&amp;utm_source=447522e9</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>274b5127202b71d7582d</t>
+        </is>
+      </c>
+      <c r="K40" t="n">
+        <v>57</v>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>role:Platform Engineer, skill:Python, skill:Bash, location:Bangalore</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>92edb3c5ff36538976a8</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Ema</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Platform Engineer</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>About Ema Ema is building the world’s leading Agentic AI platform to transform enterprise productivity. We enable organizations to delegate repetitive tasks to Ema, the Universal AI Employee, delivering 10x gains in workforce efficiency, across functions. Founded by former executives from Google, Co</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/details/5841942939?utm_medium=api&amp;utm_source=447522e9</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>5495eb964a9b85d9b44b</t>
+        </is>
+      </c>
+      <c r="K41" t="n">
+        <v>51</v>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>role:Platform Engineer, skill:Agentic AI, location:Bangalore</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>697f79c89cfd42d31537</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Teradata</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Platform Engineer</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Our Company At Teradata, we believe that people thrive when empowered with better information. Teradata Autonomous Knowledge Platform activates enterprise intelligence by unifying data, knowledge and business context to achieve tangible outcomes. With Teradata, organizations can provide agents with </t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/details/5860807556?utm_medium=api&amp;utm_source=447522e9</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>41695566aaf8ba5f1534</t>
+        </is>
+      </c>
+      <c r="K42" t="n">
+        <v>45</v>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>role:Platform Engineer, location:Bangalore</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>e2e2bcaf85a138e3e222</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Axi</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Platform Engineer</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Please note that we will only be able to accept candidates who have the appropriate rights and documentation for employment in India. Who we are. Axi is a leading global provider of margin and deliverable Foreign Exchange, Contracts for Difference (CFDs), and Financial Spread betting. Our business h</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/details/5703939765?utm_medium=api&amp;utm_source=447522e9</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>7b987ebc25ff07153a69</t>
+        </is>
+      </c>
+      <c r="K43" t="n">
+        <v>45</v>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>role:Platform Engineer, location:Bangalore</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>f0526fcb4c7d9d3cf4fc</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Cargill</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Platform Engineer</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Job Purpose and Impact The ServiceNow Senior Platform Engineer will play a critical role in designing, developing, and maintaining Cargill's ServiceNow platform to deliver scalable and reliable enterprise solutions.This position is responsible for implementing configurations, integrations, and autom</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/details/5853379748?utm_medium=api&amp;utm_source=447522e9</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>a07599f344ff8c70873d</t>
+        </is>
+      </c>
+      <c r="K44" t="n">
+        <v>45</v>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>role:Platform Engineer, location:Bangalore</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>de0945b7a98928cd69a6</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Finastra Technology</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Platform Engineer</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Who are we? At Finastra, we’re a global leader in financial services software, dedicated to expanding access to financial services and shaping what’s next for the industry. Our technology powers mission‑critical solutions across Lending, Payments and Universal Banking, supporting over 7,000 customer</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/details/5858359807?utm_medium=api&amp;utm_source=447522e9</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>759c43c17fe4627449bd</t>
+        </is>
+      </c>
+      <c r="K45" t="n">
+        <v>45</v>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>role:Platform Engineer, location:Bangalore</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>86b6124a4b8cdec681b6</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Aryaka</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Platform Engineer</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Description Platform Engineer (Java Full Stack ) As a FullStack Developer , you should have strong analytical skills, a well-rounded understanding of both front-end and back-end development, and a passion for problem-solving. Location : Bangalore, India You will have - Bachelor’s degree required. Mi</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/details/5557596032?utm_medium=api&amp;utm_source=447522e9</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>34148979a4e39eab8879</t>
+        </is>
+      </c>
+      <c r="K46" t="n">
+        <v>45</v>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>role:Platform Engineer, location:Bangalore</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>65e49cef69dea487b58a</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Kyndryl</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Platform Engineer</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Partially Remote Bangalore, Karnataka, India INEMTECH PUNE - ETZ Chennai, Tamil Nadu, India INDIVYA HYD - DIVYASHREE IN152015 NOIDA (IN152015) ARTHA INFRATE Full time R-66887 Who We Are At Kyndryl, we run and reimagine the mission-critical technology systems that drive advantage for the world's lead</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/details/5856447377?utm_medium=api&amp;utm_source=447522e9</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>2820ee427366f09ef1ec</t>
+        </is>
+      </c>
+      <c r="K47" t="n">
+        <v>45</v>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>role:Platform Engineer, location:Bangalore</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>0a6dec954ffb9ed24f97</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Agentic AI Engineer</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">This job is with HP, an inclusive employer and a member of myGwork – the largest global platform for the LGBTQ business community. Please do not contact the recruiter directly. Agentic AI Engineer Description - Job Summary This role is responsible for leading the design and execution of advanced AI </t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/land/ad/5847959683?se=WsVWIEen8RG2HomFYOMXfQ&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=44FCE51978FD48A3291A05FC0AFB8C9CBD5612B2</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>595e5ce0c414149729d2</t>
+        </is>
+      </c>
+      <c r="K48" t="n">
+        <v>86</v>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>role:AI Engineer, role:Agentic AI Engineer, skill:Agentic AI, location:Bangalore</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>7dddc21e97c0842b2af7</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Standard Chartered Bank</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>AI Engineer (India, China)</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>This job is with Standard Chartered Bank, an inclusive employer and a member of myGwork – the largest global platform for the LGBTQ business community. Please do not contact the recruiter directly. Job Summary This role could be based in India or China. When you start the application process you wil</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/land/ad/5854537872?se=WsVWIEen8RG2HomFYOMXfQ&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=71FDDD42F1439DDFA00C96C1342A4501A4014B38</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>3b8c8ab85bf42ee3a205</t>
+        </is>
+      </c>
+      <c r="K49" t="n">
+        <v>45</v>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>role:AI Engineer, location:Bangalore</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>17135c58445ee7c8f9e3</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>eBay</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>AI Platform Engineer</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>This job is with eBay, an inclusive employer and a member of myGwork – the largest global platform for the LGBTQ business community. Please do not contact the recruiter directly. At eBay, we're more than a global ecommerce leader - we're changing the way the world shops and sells. Our platform empow</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/land/ad/5857982562?se=WsVWIEen8RG2HomFYOMXfQ&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=D215B0FD12910D6EA0FB670B7E4060E2013251A2</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>003a5b09f0f9cab65bcb</t>
+        </is>
+      </c>
+      <c r="K50" t="n">
+        <v>80</v>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>role:Platform Engineer, role:AI Platform Engineer, location:Bangalore</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>cad1333a7dfcaa1bb24c</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>eBay</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>AI Platform Engineer</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>This job is with eBay, an inclusive employer and a member of myGwork – the largest global platform for the LGBTQ business community. Please do not contact the recruiter directly. At eBay, we're more than a global ecommerce leader - we're changing the way the world shops and sells. Our platform empow</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/land/ad/5857982488?se=WsVWIEen8RG2HomFYOMXfQ&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=A746E3D6C2072081EB037DB5FF89DB2B1F4A7F7A</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>003a5b09f0f9cab65bcb</t>
+        </is>
+      </c>
+      <c r="K51" t="n">
+        <v>80</v>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>role:Platform Engineer, role:AI Platform Engineer, location:Bangalore</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>8ea6531bb6da9feb3daf</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>eBay</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>AI Platform Engineer</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>This job is with eBay, an inclusive employer and a member of myGwork – the largest global platform for the LGBTQ business community. Please do not contact the recruiter directly. At eBay, we're more than a global ecommerce leader - we're changing the way the world shops and sells. Our platform empow</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/land/ad/5857251116?se=WsVWIEen8RG2HomFYOMXfQ&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=08120470A120A602552281268EC24E0672DD8DC2</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>003a5b09f0f9cab65bcb</t>
+        </is>
+      </c>
+      <c r="K52" t="n">
+        <v>80</v>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>role:Platform Engineer, role:AI Platform Engineer, location:Bangalore</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>151b019beccd94801a35</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Moody's</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Principal Software Engineer - AI</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>This job is with Moody's, an inclusive employer and a member of myGwork – the largest global platform for the LGBTQ business community. Please do not contact the recruiter directly. At Moody's, we unite the brightest minds to turn today’s risks into tomorrow’s opportunities. We do this by striving t</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/land/ad/5847959803?se=WsVWIEen8RG2HomFYOMXfQ&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=24850D9B9C940C34EAB88A822280AD413E8F4422</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>1baeb17e541bd0dce352</t>
+        </is>
+      </c>
+      <c r="K53" t="n">
+        <v>80</v>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>role:Software Engineer, role:Software Engineer - AI, location:Bangalore</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>87110fe5ce8353ff964b</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>UST</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Sr. Agentic AI Python Engineer – AI Automation &amp; Intelligent Agents | 7 Years | UST Location | Immediate Joiner</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Candidates ready to join immediately can share their details via email for quick processing.  CCTC | ECTC | Notice Period | Location Preference nitin.patil@ust.com Act fast for immediate attention! ⏳ Must-Have Skills 7 years of experience in Python Development Strong expertise in Agentic AI / Autono</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/land/ad/5864438514?se=WsVWIEen8RG2HomFYOMXfQ&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=6CDBABCC6FCDADCD4E7FD367CDEC227A5EB7F4F4</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>0aab8e46f6f471cc3b2a</t>
+        </is>
+      </c>
+      <c r="K54" t="n">
+        <v>28</v>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>skill:Python, skill:LLM, skill:Agentic AI, location:Bangalore</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>aef0c423e91fa86ca69c</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Dentsu Global Services</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Engineering Lead (AI &amp; Automation Products)</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Technical Architecture &amp; Delivery Lead architecture decisions across the portfolio — schema design, API contracts, integration patterns, workflow orchestration, and when to integrate via direct API versus MCP (Model Context Protocol), weighing latency, control, security, auditability, and reusabilit</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/land/ad/5864432860?se=WsVWIEen8RG2HomFYOMXfQ&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=2180590FC5B2E91749343A571B5B817D66D0042B</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>47741df21b60fcea7e80</t>
+        </is>
+      </c>
+      <c r="K55" t="n">
+        <v>28</v>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>skill:MCP, skill:Model Context Protocol, skill:Workflow Orchestration, location:Bangalore</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>4428dbb716a41e6147db</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Leadrat</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Company Profile LeadRat CRM is a fast-growing SaaS company providing CRM and sales automation solutions for the real estate industry. With offices in Bengaluru, Pune, Gurugram, and Dubai , we are building innovative AI-powered products that help businesses automate, scale, and grow. AI Engineer – LL</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/details/5832769922?utm_medium=api&amp;utm_source=447522e9</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>a56d196f9f7633e247dc</t>
+        </is>
+      </c>
+      <c r="K56" t="n">
+        <v>51</v>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>role:AI Engineer, skill:LLM, location:Bangalore</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>d0bf7738c7e0a7bb100b</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>NextNation</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Location: Onsite - HSR Layout, Bangalore Experience: Fresher to 1.5 Years Website - https://nextnation.co Company Description Company Description NextNation is a global talent mobility company specializing in comprehensive immigration solutions. We empower individuals to pursue international career </t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/details/5859083849?utm_medium=api&amp;utm_source=447522e9</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>1f5e579c2c65932c53f8</t>
+        </is>
+      </c>
+      <c r="K57" t="n">
+        <v>53</v>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>role:AI Engineer, location:Bangalore, experience:fresher</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>78a6d7560ddbd4caa774</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Acme Services Private Limited</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Richmond Town, Bangalore</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Job Description: Build application-facing AI features powered by LLMs, agentic workflows, and AI orchestration platforms. Integrate with MLOps-managed agents and consume LLM capabilities through AI Gateway patterns including routing, authentication, policy controls, and logging. Design and implement</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/details/5863107008?utm_medium=api&amp;utm_source=447522e9</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>3337532b20885bd1775f</t>
+        </is>
+      </c>
+      <c r="K58" t="n">
+        <v>69</v>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>role:AI Engineer, skill:LLM, skill:MCP, skill:AI Orchestration, skill:Tool Calling, location:Bangalore</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>f65350a6483821dfdd3a</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Acme Services Private Limited</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Richmond Town, Bangalore</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Job Description: Build and deploy production-grade AI and Agentic AI solutions for client business use cases. Design and implement AI agent workflows using LangGraph, CrewAI, and cloud-based agent platforms. Develop and manage AI/ML pipelines, including RAG, multi-agent orchestration, evaluation, an</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/details/5865169480?utm_medium=api&amp;utm_source=447522e9</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>1463f44c91d7b4c9c45f</t>
+        </is>
+      </c>
+      <c r="K59" t="n">
+        <v>81</v>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>role:AI Engineer, skill:MCP, skill:RAG, skill:Multi-Agent Systems, skill:Agentic AI, skill:AI Agents, skill:Observability, location:Bangalore</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2b8e483682cf248f4942</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Mopid</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Hiring: AI Engineers | Bangalore Bangalore | 100% In-office ₹25–35 LPA — AI Engineer ₹35–45 LPA — Senior AI Engineer Immediate joiners preferred We’re hiring for a Decision Intelligence company building the next generation of AI infrastructure for enterprise and institutional decision-making. The co</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/details/5862885220?utm_medium=api&amp;utm_source=447522e9</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>dd293c2a7f9ccdc96af8</t>
+        </is>
+      </c>
+      <c r="K60" t="n">
+        <v>45</v>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>role:AI Engineer, location:Bangalore</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>65e2ba08bd23aa40c771</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Stealth AI</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Kenchanahalli, Bangalore</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Hiring: AI Engineers | Bangalore  Bangalore | 100% In-office  ₹25–35 LPA — AI Engineer  ₹35–45 LPA — Senior AI Engineer  Immediate joiners preferred We’re hiring for a Decision Intelligence company building the next generation of AI infrastructure for enterprise and institutional decision-making. T</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/details/5863765990?utm_medium=api&amp;utm_source=447522e9</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>53cf344cddff2e39d480</t>
+        </is>
+      </c>
+      <c r="K61" t="n">
+        <v>45</v>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>role:AI Engineer, location:Bangalore</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>859a59a8de744133282b</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Top Gen AI Jobs</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Home/Jobs/AI Engineer AI Engineer Parexel Hyderabad / Bengaluru / Mohali 3 years Today $26.5K–42.2K/yr Full-time Onsite Skills Required LLM OpenAI Anthropic LangChain LangGraph AWS S3 Lambda IAM AWS Bedrock NLP Python MedDRA ICH E2B(R3) MCP Description Parexel is seeking an AI Engineer for agent and</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/details/5848585266?utm_medium=api&amp;utm_source=447522e9</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>1121c1519fdd802e5f6c</t>
+        </is>
+      </c>
+      <c r="K62" t="n">
+        <v>63</v>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>role:AI Engineer, skill:Python, skill:LLM, skill:MCP, location:Bangalore</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>758e789b17e2f7dd6c51</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Jothishi Online and Advertising Services Private Limited</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>AI ENGINEER – RETROGRADE AI Generative AI | LLMs | RAG | AI Agents | Vedic Astrology Company: JOTHISHI Online &amp; Advertising Services Pvt. Ltd. Product: RetroGrade AI Website: https://retrograde.co.in/ Location: Bengaluru / Hybrid / Remote Employment: Full-Time About RetroGrade AI RetroGrade AI , fro</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/details/5842544539?utm_medium=api&amp;utm_source=447522e9</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>088a26264467b471f752</t>
+        </is>
+      </c>
+      <c r="K63" t="n">
+        <v>57</v>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>role:AI Engineer, skill:RAG, skill:AI Agents, location:Bangalore</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>d8522750bd2d5068740c</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>MyData Insights Private Limited</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>AI engineer</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Description We are looking for a talented AI Engineer to join MyData Insights Private Limited, a leading company in the Information Technology sector. As an AI Engineer, you will play a crucial role in developing and implementing cutting-edge artificial intelligence solutions. Your work will be inst</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/details/5503837785?utm_medium=api&amp;utm_source=447522e9</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>33311190bd5f9f970705</t>
+        </is>
+      </c>
+      <c r="K64" t="n">
+        <v>45</v>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>role:AI Engineer, location:Bangalore</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>fd94b9c410b00a90bc80</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Wirelane</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Embedded Software Engineer IoT &amp; Connectivity (m/w/d)</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>München</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>&lt;br&gt;&lt;strong&gt;Willkommen bei Wirelane&lt;/strong&gt;&lt;p&gt;Deutschland verzeichnet neue Rekordzulassungszahlen von Elektrofahrzeugen sowie eine rasant steigende Zahl von Lademöglichkeiten. Die Bundesregierung hat sich in diesem Kontext sehr ambitionierte Ziele gesetzt und möchte bis zum Jahr 2030 15 Millionen z</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/wirelane/embedded-software-engineer-iot-connectivity-munchen-3116</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>7fd5c61c5bc356934e7f</t>
+        </is>
+      </c>
+      <c r="K65" t="n">
+        <v>41</v>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>role:Software Engineer, skill:Python</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>99d4f879ad8b76870f96</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Speechify</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Software Engineer, Platform - Munich, Germany</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Munich, Bavaria, Germany</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;The mission of Speechify is to make sure that reading is never a barrier to learning.&lt;/p&gt;
+&lt;p&gt;Over 50 million people use Speechify's text-to-speech products to turn whatever they're reading – PDFs, books, Google Docs, news articles, websites – into audio, so they can read faster, read more, and re</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/speechify/software-engineer-platform-munich-germany-477527</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>b02474cd3a4ce0de2b27</t>
+        </is>
+      </c>
+      <c r="K66" t="n">
+        <v>35</v>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>role:Software Engineer</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>68eaf78c00d9766c64f8</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Speechify</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Software Engineer, Data Infrastructure &amp; Acquisition - Frankfurt, Germany</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Frankfurt, Hesse, Germany</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;The mission of Speechify is to make sure that reading is never a barrier to learning.&lt;/p&gt;
+&lt;p&gt;Over 50 million people use Speechify's text-to-speech products to turn whatever they're reading – PDFs, books, Google Docs, news articles, websites – into audio, so they can read faster, read more, and re</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/speechify/software-engineer-data-infrastructure-acquisition-frankfurt-germany-297787</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>f0b4c3a2a3f9c8cc7053</t>
+        </is>
+      </c>
+      <c r="K67" t="n">
+        <v>47</v>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>role:Software Engineer, skill:Python, skill:Bash</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>12bea8251754f5d6849c</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Speechify</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Software Engineer, Data Infrastructure &amp; Acquisition - Berlin, Germany</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Berlin, Germany</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;The mission of Speechify is to make sure that reading is never a barrier to learning.&lt;/p&gt;
+&lt;p&gt;Over 50 million people use Speechify's text-to-speech products to turn whatever they're reading – PDFs, books, Google Docs, news articles, websites – into audio, so they can read faster, read more, and re</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/speechify/software-engineer-data-infrastructure-acquisition-berlin-germany-91842</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>02b12e9d321eb7782c46</t>
+        </is>
+      </c>
+      <c r="K68" t="n">
+        <v>47</v>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>role:Software Engineer, skill:Python, skill:Bash</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>bc5b87159dc21e935c42</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Speechify</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Software Engineer, Platform - Cologne, Germany</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Cologne, North Rhine-Westphalia, Germany</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;The mission of Speechify is to make sure that reading is never a barrier to learning.&lt;/p&gt;
+&lt;p&gt;Over 50 million people use Speechify's text-to-speech products to turn whatever they're reading – PDFs, books, Google Docs, news articles, websites – into audio, so they can read faster, read more, and re</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/speechify/software-engineer-platform-cologne-germany-147673</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>31d13ef79c73b6982bbb</t>
+        </is>
+      </c>
+      <c r="K69" t="n">
+        <v>35</v>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>role:Software Engineer</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>48bd105440f8cda2bf9f</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Elastic</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Full Stack - Web Engineering</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>&amp;lt;div class=&amp;quot;content-intro&amp;quot;&amp;gt;&amp;lt;p&amp;gt;Elastic, the Search AI Company, enables everyone to find the answers they need in real time, using all their data, at scale — unleashing the potential of businesses and people. The Elastic Search AI Platform, used by more than 50% of the Fortune 50</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/elastic/software-engineer-ii-full-stack-web-engineering-462983</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>d455ca70c1c288d84aac</t>
+        </is>
+      </c>
+      <c r="K70" t="n">
+        <v>59</v>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>role:Software Engineer, skill:Python, skill:TypeScript, skill:GitHub, skill:Observability</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>263b87db3ba70d52c595</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Elastic</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Software Engineer II - EDR Workflows - Security</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>&amp;lt;div class=&amp;quot;content-intro&amp;quot;&amp;gt;&amp;lt;p&amp;gt;Elastic, the Search AI Company, enables everyone to find the answers they need in real time, using all their data, at scale — unleashing the potential of businesses and people. The Elastic Search AI Platform, used by more than 50% of the Fortune 50</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/elastic/software-engineer-ii-edr-workflows-security-390663</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>29774c5a2f7287562f1d</t>
+        </is>
+      </c>
+      <c r="K71" t="n">
+        <v>47</v>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>role:Software Engineer, skill:TypeScript, skill:Observability</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>5fc4191db20659cfe89e</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>dataiku</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Fullstack Software Engineer - Core</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>&amp;lt;div class=&amp;quot;content-intro&amp;quot;&amp;gt;&amp;lt;p&amp;gt;&amp;lt;a href=&amp;quot;https://www.dataiku.com/?utm_source=newswire&amp;amp;amp;utm_medium=press-release&amp;amp;amp;utm_campaign=PlatformforAISuccess&amp;quot; target=&amp;quot;_blank&amp;quot;&amp;gt;Dataiku&amp;lt;/a&amp;gt; is the Platform for AI Success, the enterprise orchestrati</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/dataiku/remote-fullstack-software-engineer-core-184220</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>491ae80d37b5603e1ed9</t>
+        </is>
+      </c>
+      <c r="K72" t="n">
+        <v>73</v>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>role:Software Engineer, skill:Python, skill:SQL, skill:GitHub, skill:LLM, skill:AI Agents, experience:junior</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>e4fdd346204e41c99447</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>mozilla</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Software Engineer, Release Engineering</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>&amp;lt;div class=&amp;quot;gmail_default&amp;quot; style=&amp;quot;font-size: small;&amp;quot;&amp;gt;
+&amp;lt;div&amp;gt;
+&amp;lt;p&amp;gt;&amp;lt;strong&amp;gt;Why Mozilla?&amp;lt;/strong&amp;gt;&amp;lt;/p&amp;gt;
+&amp;lt;p&amp;gt;&amp;lt;span style=&amp;quot;font-weight: 400;&amp;quot;&amp;gt;Mozilla Corporation is the non-profit-backed technology company that has shaped the intern</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/mozilla/software-engineer-release-engineering-177435</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>3ba913b9ae12d9762171</t>
+        </is>
+      </c>
+      <c r="K73" t="n">
+        <v>41</v>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>role:Software Engineer, skill:Python</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>9ecf8d39387647ce96d3</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>toogoodtogo</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Frontend Software Engineer</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>&amp;lt;p&amp;gt;At Too Good To Go, we have an ambitious goal: to inspire and empower everyone to fight food waste together.&amp;lt;/p&amp;gt;
+&amp;lt;p&amp;gt;40% of all food produced in the world is wasted. And that has a huge impact on the health of our planet, with 10% of greenhouse gas emissions coming from food waste</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.co.uk/jobs/companies/toogoodtogo/frontend-software-engineer-london-96025</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>arbeitnow</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>31200b1ce5ac1c2e2ffd</t>
+        </is>
+      </c>
+      <c r="K74" t="n">
+        <v>59</v>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>role:Software Engineer, skill:JavaScript, skill:TypeScript, skill:Git, skill:Vite</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
           <t>ea727cfe696841aa3edf</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B75" t="inlineStr">
         <is>
           <t>Oracle</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C75" t="inlineStr">
         <is>
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr">
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr">
         <is>
           <t>https://careers.oracle.com/en/sites/jobsearch/jobs?keyword=Software%20Engineer&amp;location=United%20States&amp;locationId=300000000149325</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G75" t="inlineStr">
         <is>
           <t>generic</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H75" t="inlineStr">
         <is>
           <t>2026-09-02 15:14:08</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2026-09-03 01:57:07</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:26:15</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
         <is>
           <t>9a55c6d446a7838dea8c</t>
         </is>
       </c>
-      <c r="K2" t="n">
+      <c r="K75" t="n">
         <v>35</v>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="L75" t="inlineStr">
         <is>
           <t>role:Software Engineer</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
